--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Kachchh.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/Kachchh.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940A1DCC-253B-44D7-97C9-3F7AF7A0BEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AD6DDC-926A-41C4-AB10-5C319D7D0293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="90">
   <si>
     <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                  CENTRAL                                                                                      </t>
   </si>
@@ -564,29 +564,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -610,24 +628,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -912,143 +912,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-    </row>
-    <row r="2" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
+    <row r="2" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+    </row>
+    <row r="3" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+    </row>
+    <row r="4" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="21">
         <v>16</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12">
+      <c r="E4" s="21"/>
+      <c r="F4" s="21">
         <v>20</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12">
+      <c r="G4" s="21"/>
+      <c r="H4" s="21">
         <v>6</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12">
+      <c r="I4" s="21"/>
+      <c r="J4" s="21">
         <v>16</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12">
+      <c r="K4" s="21"/>
+      <c r="L4" s="21">
         <v>16</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12">
+      <c r="M4" s="21"/>
+      <c r="N4" s="21">
         <v>4</v>
       </c>
-      <c r="O4" s="12"/>
+      <c r="O4" s="21"/>
       <c r="P4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="14" t="s">
+    <row r="5" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14" t="s">
+      <c r="I5" s="16"/>
+      <c r="J5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14" t="s">
+      <c r="K5" s="16"/>
+      <c r="L5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14" t="s">
+      <c r="M5" s="16"/>
+      <c r="N5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="14"/>
+      <c r="O5" s="16"/>
       <c r="P5" s="8">
         <f>SUM(D4:O4)</f>
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1096,14 +1096,14 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+    <row r="7" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="9">
@@ -1132,14 +1132,14 @@
       <c r="O7" s="9"/>
       <c r="P7" s="8"/>
     </row>
-    <row r="8" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="9"/>
@@ -1162,14 +1162,14 @@
       <c r="O8" s="9"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+    <row r="9" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="10" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="9">
@@ -1194,14 +1194,14 @@
       <c r="O9" s="9"/>
       <c r="P9" s="8"/>
     </row>
-    <row r="10" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+    <row r="10" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="9"/>
@@ -1230,14 +1230,14 @@
       </c>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+    <row r="11" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="9"/>
@@ -1262,14 +1262,14 @@
       <c r="O11" s="6"/>
       <c r="P11" s="8"/>
     </row>
-    <row r="12" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="10" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="9">
@@ -1294,14 +1294,14 @@
       <c r="O12" s="6"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="9">
@@ -1328,14 +1328,14 @@
       <c r="O13" s="6"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+    <row r="14" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="10" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="9"/>
@@ -1364,14 +1364,14 @@
       <c r="O14" s="6"/>
       <c r="P14" s="8"/>
     </row>
-    <row r="15" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+    <row r="15" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="10" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="9"/>
@@ -1394,14 +1394,14 @@
       <c r="O15" s="6"/>
       <c r="P15" s="8"/>
     </row>
-    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="10" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="9">
@@ -1428,14 +1428,14 @@
       <c r="O16" s="6"/>
       <c r="P16" s="8"/>
     </row>
-    <row r="17" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+    <row r="17" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="10" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="9">
@@ -1458,14 +1458,14 @@
       <c r="O17" s="6"/>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+    <row r="18" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="9">
@@ -1490,14 +1490,14 @@
       <c r="O18" s="6"/>
       <c r="P18" s="8"/>
     </row>
-    <row r="19" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="10" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="9"/>
@@ -1532,14 +1532,14 @@
       </c>
       <c r="P19" s="8"/>
     </row>
-    <row r="20" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+    <row r="20" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="10" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="9">
@@ -1568,12 +1568,12 @@
       <c r="O20" s="9"/>
       <c r="P20" s="8"/>
     </row>
-    <row r="21" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
       <c r="D21" s="5">
         <f>SUM(D7:D20)</f>
         <v>16</v>
@@ -1609,31 +1609,31 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-    </row>
-    <row r="23" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+    </row>
+    <row r="23" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -1657,11 +1657,11 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
     </row>
-    <row r="24" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -1685,11 +1685,11 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -1713,11 +1713,11 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -1741,11 +1741,11 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -1769,11 +1769,11 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -1797,7 +1797,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>50</v>
       </c>
@@ -1825,7 +1825,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>50</v>
       </c>
@@ -1853,7 +1853,7 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>50</v>
       </c>
@@ -1881,11 +1881,11 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="13" t="s">
         <v>59</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -1909,11 +1909,11 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -1937,12 +1937,12 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
       <c r="D34" s="5">
         <v>0</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1994,12 +1994,12 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+    <row r="36" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A36" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
       <c r="D36" s="5">
         <f>+D21+D33</f>
         <v>16</v>
@@ -2037,16 +2037,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:P22"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:P3"/>
@@ -2058,6 +2048,16 @@
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:P22"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2066,142 +2066,142 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-    </row>
-    <row r="2" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
+    <row r="2" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+    </row>
+    <row r="4" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="22" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="21">
         <v>10</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12">
+      <c r="E4" s="21"/>
+      <c r="F4" s="21">
         <v>14</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="24">
+      <c r="G4" s="21"/>
+      <c r="H4" s="30">
         <v>4</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="J4" s="12">
+      <c r="I4" s="31"/>
+      <c r="J4" s="21">
         <v>8</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12">
+      <c r="K4" s="21"/>
+      <c r="L4" s="21">
         <v>8</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12">
+      <c r="M4" s="21"/>
+      <c r="N4" s="21">
         <v>0</v>
       </c>
-      <c r="O4" s="12"/>
+      <c r="O4" s="21"/>
       <c r="P4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="14" t="s">
+    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="26" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="27"/>
-      <c r="J5" s="14" t="s">
+      <c r="I5" s="23"/>
+      <c r="J5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14" t="s">
+      <c r="K5" s="16"/>
+      <c r="L5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14" t="s">
+      <c r="M5" s="16"/>
+      <c r="N5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="14"/>
+      <c r="O5" s="16"/>
       <c r="P5" s="1">
         <f>SUM(D4:O4)</f>
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -2223,8 +2223,12 @@
       <c r="G6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="J6" s="2" t="s">
         <v>10</v>
       </c>
@@ -2245,7 +2249,7 @@
       </c>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>51</v>
       </c>
@@ -2277,7 +2281,7 @@
       <c r="O7" s="9"/>
       <c r="P7" s="8"/>
     </row>
-    <row r="8" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>51</v>
       </c>
@@ -2313,7 +2317,7 @@
       <c r="O8" s="9"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>52</v>
       </c>
@@ -2341,7 +2345,7 @@
       <c r="O9" s="9"/>
       <c r="P9" s="8"/>
     </row>
-    <row r="10" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>52</v>
       </c>
@@ -2373,7 +2377,7 @@
       <c r="O10" s="9"/>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>53</v>
       </c>
@@ -2405,7 +2409,7 @@
       <c r="O11" s="9"/>
       <c r="P11" s="8"/>
     </row>
-    <row r="12" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>54</v>
       </c>
@@ -2433,7 +2437,7 @@
       <c r="O12" s="9"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>55</v>
       </c>
@@ -2461,7 +2465,7 @@
       <c r="O13" s="9"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>50</v>
       </c>
@@ -2489,7 +2493,7 @@
       <c r="O14" s="9"/>
       <c r="P14" s="8"/>
     </row>
-    <row r="15" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>50</v>
       </c>
@@ -2525,7 +2529,7 @@
       <c r="O15" s="9"/>
       <c r="P15" s="8"/>
     </row>
-    <row r="16" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>56</v>
       </c>
@@ -2561,7 +2565,7 @@
       <c r="O16" s="9"/>
       <c r="P16" s="8"/>
     </row>
-    <row r="17" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>57</v>
       </c>
@@ -2589,7 +2593,7 @@
       <c r="O17" s="9"/>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>57</v>
       </c>
@@ -2617,7 +2621,7 @@
       <c r="O18" s="9"/>
       <c r="P18" s="8"/>
     </row>
-    <row r="19" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="18" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>57</v>
       </c>
@@ -2645,12 +2649,12 @@
       <c r="O19" s="9"/>
       <c r="P19" s="8"/>
     </row>
-    <row r="20" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+    <row r="20" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A20" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
       <c r="D20" s="5">
         <f>SUM(D7:D19)</f>
         <v>10</v>
@@ -2686,32 +2690,32 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
-    </row>
-    <row r="22" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+    </row>
+    <row r="22" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A22" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="17"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="5">
         <v>0</v>
       </c>
@@ -2738,12 +2742,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:16" ht="18" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="5">
         <f>+D20+D22</f>
         <v>10</v>
@@ -2780,16 +2784,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A21:P21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H5:I5"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:P3"/>
@@ -2801,6 +2795,16 @@
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A21:P21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
